--- a/InputFiles/CTDC/TC01_CTDC_Sex-Male.xlsx
+++ b/InputFiles/CTDC/TC01_CTDC_Sex-Male.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sohilz2/Automation/10-23-2025/Commons_Automation/InputFiles/CTDC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epishinavv/git/Commons_Automation/InputFiles/CTDC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5288B7CE-CC49-6943-928D-F7D253E9977B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0131E6B6-84D5-0643-AA24-28E4BCB41ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-39060" yWindow="-380" windowWidth="30240" windowHeight="24500" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="20980" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -162,7 +162,49 @@
     <t>FilesTab</t>
   </si>
   <si>
+    <t>SELECT 
+    COUNT(DISTINCT std.study_id) AS Studies,
+    COUNT(DISTINCT prt.participant_id) AS Participants,
+    COUNT(DISTINCT dgn.ctep_disease_term) AS Diagnoses,
+    COUNT(DISTINCT tgt.targeted_therapy) AS "Targeted Therapies",
+    COUNT(DISTINCT bio.specimen_record_id) AS Biospecimens,
+    COUNT(DISTINCT fil.data_file_uuid) AS Files
+FROM 
+    df_study std
+LEFT JOIN 
+    df_participant prt 
+        ON std.study_short_name = prt."study.study_short_name"
+LEFT JOIN 
+    df_diagnosis dgn 
+        ON prt.participant_id = dgn."participant.participant_id"
+LEFT JOIN 
+    df_demographic demo 
+        ON prt.participant_id = demo."participant.participant_id"
+LEFT JOIN 
+    df_exposure exp 
+        ON prt.participant_id = exp."participant.participant_id"
+LEFT JOIN 
+    df_targeted_therapy tgt 
+        ON prt.participant_id = tgt."participant.participant_id"
+LEFT JOIN 
+    df_non_targeted_therapy ntt 
+        ON prt.participant_id = ntt."participant.participant_id"
+LEFT JOIN 
+    df_participant_status pst 
+        ON prt.participant_id = pst."participant.participant_id"
+LEFT JOIN 
+    df_biospecimen bio 
+        ON prt.participant_id = bio."participant.participant_id"
+LEFT JOIN 
+    df_file fil 
+        ON prt.participant_id = fil."participant.participant_id"
+WHERE 
+    std.study_id = 'NCT04314401'
+    AND demo.sex = 'Male';</t>
+  </si>
+  <si>
     <t>SELECT DISTINCT
+std.study_accession as "Study Accession",  
     fil.data_file_name AS "File Name",
     fil.data_file_format AS "Format",
     fil.data_file_type AS "File Type",
@@ -228,47 +270,6 @@
 WHERE 
     std.study_id = 'NCT04314401' AND demo.sex = 'Male' AND fil.data_file_name IS NOT NULL
 LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT 
-    COUNT(DISTINCT std.study_id) AS Studies,
-    COUNT(DISTINCT prt.participant_id) AS Participants,
-    COUNT(DISTINCT dgn.ctep_disease_term) AS Diagnoses,
-    COUNT(DISTINCT tgt.targeted_therapy) AS "Targeted Therapies",
-    COUNT(DISTINCT bio.specimen_record_id) AS Biospecimens,
-    COUNT(DISTINCT fil.data_file_uuid) AS Files
-FROM 
-    df_study std
-LEFT JOIN 
-    df_participant prt 
-        ON std.study_short_name = prt."study.study_short_name"
-LEFT JOIN 
-    df_diagnosis dgn 
-        ON prt.participant_id = dgn."participant.participant_id"
-LEFT JOIN 
-    df_demographic demo 
-        ON prt.participant_id = demo."participant.participant_id"
-LEFT JOIN 
-    df_exposure exp 
-        ON prt.participant_id = exp."participant.participant_id"
-LEFT JOIN 
-    df_targeted_therapy tgt 
-        ON prt.participant_id = tgt."participant.participant_id"
-LEFT JOIN 
-    df_non_targeted_therapy ntt 
-        ON prt.participant_id = ntt."participant.participant_id"
-LEFT JOIN 
-    df_participant_status pst 
-        ON prt.participant_id = pst."participant.participant_id"
-LEFT JOIN 
-    df_biospecimen bio 
-        ON prt.participant_id = bio."participant.participant_id"
-LEFT JOIN 
-    df_file fil 
-        ON prt.participant_id = fil."participant.participant_id"
-WHERE 
-    std.study_id = 'NCT04314401'
-    AND demo.sex = 'Male';</t>
   </si>
 </sst>
 </file>
@@ -732,8 +733,8 @@
       <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>13</v>
+      <c r="C2" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>6</v>
@@ -754,8 +755,8 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>12</v>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="2"/>
     </row>
